--- a/Book2.xlsx
+++ b/Book2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pwkut\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45AA3D84-E79D-4849-93CD-96C4D2457A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{730FECEA-E506-4832-9DC7-5577CCD6172C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="1" xr2:uid="{5ED3BFE2-4C55-4B66-81F1-70B76F13713E}"/>
   </bookViews>
@@ -122,12 +122,13 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{66B616BC-A4F3-4ADE-9100-38A6D218C8A8}" name="Table2" displayName="Table2" ref="A1:B5" totalsRowShown="0">
-  <autoFilter ref="A1:B5" xr:uid="{66B616BC-A4F3-4ADE-9100-38A6D218C8A8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{66B616BC-A4F3-4ADE-9100-38A6D218C8A8}" name="Table2" displayName="Table2" ref="A1:B4" totalsRowShown="0">
+  <autoFilter ref="A1:B4" xr:uid="{66B616BC-A4F3-4ADE-9100-38A6D218C8A8}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{76EC1407-7957-4F4C-8663-9ADB29B5BE58}" name="ID"/>
     <tableColumn id="2" xr3:uid="{FEB4BD9E-DAD3-4F9C-9A37-8DF0377C3852}" name="Column1" dataDxfId="0">
       <calculatedColumnFormula>Table2[[#This Row],[ID]]+13
+-5
 /2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -494,7 +495,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8D93652-4451-4228-BF43-0C8DD3F27027}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -511,8 +512,9 @@
       </c>
       <c r="B2">
         <f>Table2[[#This Row],[ID]]+13
+-5
 /2</f>
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -521,28 +523,20 @@
       </c>
       <c r="B3">
         <f>Table2[[#This Row],[ID]]+13
+-5
 /2</f>
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4">
         <f>Table2[[#This Row],[ID]]+13
+-5
 /2</f>
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <f>Table2[[#This Row],[ID]]+13
-/2</f>
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
     </row>
   </sheetData>
